--- a/src/TestData/Issue461.xlsx
+++ b/src/TestData/Issue461.xlsx
@@ -35,12 +35,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -61,6 +63,12 @@
       <c r="D1" s="4">
         <v>44927</v>
       </c>
+      <c r="E1" s="5">
+        <v>44927</v>
+      </c>
+      <c r="F1" s="6">
+        <v>44927</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
